--- a/config/液冷机组/水冷机组_埃森特.xlsx
+++ b/config/液冷机组/水冷机组_埃森特.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <t>AB</t>
   </si>
   <si>
-    <t>ambientTemperature</t>
+    <t>ambientT</t>
   </si>
   <si>
     <t>{"en":"ambient temperature"}</t>
@@ -105,7 +105,7 @@
     <t>回液温度</t>
   </si>
   <si>
-    <t>returnLiquidTemperature</t>
+    <t>returnLiquidT</t>
   </si>
   <si>
     <t>{"en":"Return liquid temperature"}</t>
@@ -114,7 +114,7 @@
     <t>供液温度</t>
   </si>
   <si>
-    <t>liquidSupplyTemperature</t>
+    <t>liquidSupplyT</t>
   </si>
   <si>
     <t>{"en":"Liquid supply temperature"}</t>
@@ -150,7 +150,7 @@
     <t>共45挡，0挡表示停止，1挡为最低转速，45挡为最高转速</t>
   </si>
   <si>
-    <t>system1FanGear</t>
+    <t>sys1FanGear</t>
   </si>
   <si>
     <t>{"en":"System 1 fan gear"}</t>
@@ -165,7 +165,7 @@
     <t>EC风机为目标转速（%），AC风机为反馈转速（rps）</t>
   </si>
   <si>
-    <t>system1FirstGroupFanSpeed</t>
+    <t>sys1FirstGroupFanSpeed</t>
   </si>
   <si>
     <t>{"en":"System 1 first group fan speed"}</t>
@@ -174,7 +174,7 @@
     <t>系统1第二组风机转速</t>
   </si>
   <si>
-    <t>system1SecondGroupFanSpeed</t>
+    <t>sys1SecondGroupFanSpeed</t>
   </si>
   <si>
     <t>{"en":"System 1 second group fan speed"}</t>
@@ -189,7 +189,7 @@
     <t>EC风机为目标转速（%），AC风机为电流（A）</t>
   </si>
   <si>
-    <t>system1ThirdGroupFanSpeedSystem1FanCurrent</t>
+    <t>sys1ThirdGroupFanSpeedSys1FanCurr</t>
   </si>
   <si>
     <t>{"en":"System 1 third group fan speed/System 1 fan current"}</t>
@@ -198,7 +198,7 @@
     <t>系统1压缩机状态</t>
   </si>
   <si>
-    <t>system1CompressorStatus</t>
+    <t>sys1CompressorStat</t>
   </si>
   <si>
     <t>{"en":"System 1 Compressor Status"}</t>
@@ -220,7 +220,7 @@
     <t>Hz</t>
   </si>
   <si>
-    <t>system1CompressorTargetFrequency</t>
+    <t>sys1CompressorTargetFreq</t>
   </si>
   <si>
     <t>{"en":"System 1 Compressor Target Frequency"}</t>
@@ -229,7 +229,7 @@
     <t>系统1压缩机运行频率</t>
   </si>
   <si>
-    <t>system1CompressorOperatingFrequency</t>
+    <t>sys1CompressorOperatingFreq</t>
   </si>
   <si>
     <t>{"en":"System 1 Compressor Operating Frequency"}</t>
@@ -238,7 +238,7 @@
     <t>系统1电子膨胀阀开度</t>
   </si>
   <si>
-    <t>system1ElectronicExpansionValveOpening</t>
+    <t>sys1ElectronicExpansionValveOpening</t>
   </si>
   <si>
     <t>{"en":"System 1 Electronic Expansion Valve Opening"}</t>
@@ -247,7 +247,7 @@
     <t>系统2压缩机状态</t>
   </si>
   <si>
-    <t>system2CompressorStatus</t>
+    <t>sys2CompressorStat</t>
   </si>
   <si>
     <t>{"en":"System 2 Compressor Status"}</t>
@@ -256,7 +256,7 @@
     <t>系统2压缩机目标频率</t>
   </si>
   <si>
-    <t>targetFrequencyOfSystem2Compressor</t>
+    <t>targetFreqOfSys2Compressor</t>
   </si>
   <si>
     <t>{"en":"Target frequency of system 2 compressor"}</t>
@@ -265,7 +265,7 @@
     <t>系统2压缩机运行频率</t>
   </si>
   <si>
-    <t>system2CompressorOperatingFrequency</t>
+    <t>sys2CompressorOperatingFreq</t>
   </si>
   <si>
     <t>{"en":"System 2 Compressor Operating Frequency"}</t>
@@ -274,7 +274,7 @@
     <t>系统2电子膨胀阀开度</t>
   </si>
   <si>
-    <t>system2ElectronicExpansionValveOpening</t>
+    <t>sys2ElectronicExpansionValveOpening</t>
   </si>
   <si>
     <t>{"en":"System 2 Electronic Expansion Valve Opening"}</t>
@@ -427,7 +427,7 @@
     <t>系统2风机挡位</t>
   </si>
   <si>
-    <t>system2FanGear</t>
+    <t>sys2FanGear</t>
   </si>
   <si>
     <t>{"en":"System 2 fan gear"}</t>
@@ -436,7 +436,7 @@
     <t>系统2第一组风机转速</t>
   </si>
   <si>
-    <t>system2FirstGroupFanSpeed</t>
+    <t>sys2FirstGroupFanSpeed</t>
   </si>
   <si>
     <t>{"en":"System 2 first group fan speed"}</t>
@@ -445,7 +445,7 @@
     <t>系统2第二组风机转速</t>
   </si>
   <si>
-    <t>system2SecondGroupFanSpeed</t>
+    <t>sys2SecondGroupFanSpeed</t>
   </si>
   <si>
     <t>{"en":"System 2 second group fan speed"}</t>
@@ -454,7 +454,7 @@
     <t>系统2第三组风机转速/系统2风机电流</t>
   </si>
   <si>
-    <t>system2ThirdGroupFanSpeedSystem2FanCurrent</t>
+    <t>sys2ThirdGroupFanSpeedSys2FanCurr</t>
   </si>
   <si>
     <t>{"en":"System 2 third group fan speed/System 2 fan current"}</t>
@@ -466,7 +466,7 @@
     <t>HoldingRegisters</t>
   </si>
   <si>
-    <t>unitPowerOnOffEnable</t>
+    <t>unitPwrOnOffEn</t>
   </si>
   <si>
     <t>{"en":"Unit power on/off enable"}</t>
@@ -479,7 +479,7 @@
     <t>机组运行功能选择</t>
   </si>
   <si>
-    <t>unitOperationFunctionSelection</t>
+    <t>unitOpFuncSel</t>
   </si>
   <si>
     <t>{"en":"Unit operation function selection"}</t>
@@ -494,7 +494,7 @@
     <t>制冷设定出水温度</t>
   </si>
   <si>
-    <t>coolingSetWaterOutletTemperature</t>
+    <t>coolSetWaterOutT</t>
   </si>
   <si>
     <t>{"en":"Cooling set water outlet temperature"}</t>
@@ -503,7 +503,7 @@
     <t>制冷设定回水温度</t>
   </si>
   <si>
-    <t>refrigerationSetReturnWaterTemperature</t>
+    <t>refrigSetReturnWaterT</t>
   </si>
   <si>
     <t>{"en":"Refrigeration set return water temperature"}</t>
@@ -512,7 +512,7 @@
     <t>加热设定出水温度</t>
   </si>
   <si>
-    <t>heatingSetWaterOutletTemperature</t>
+    <t>heatSetWaterOutT</t>
   </si>
   <si>
     <t>{"en":"Heating set water outlet temperature"}</t>
@@ -521,7 +521,7 @@
     <t>加热设定回水温度</t>
   </si>
   <si>
-    <t>heatingSetReturnWaterTemperature</t>
+    <t>heatSetReturnWaterT</t>
   </si>
   <si>
     <t>{"en":"Heating set return water temperature"}</t>
@@ -530,7 +530,7 @@
     <t>制冷停止温差</t>
   </si>
   <si>
-    <t>coolingStopTemperatureDifference</t>
+    <t>coolStopTDiff</t>
   </si>
   <si>
     <t>{"en":"Cooling stop temperature difference"}</t>
@@ -539,7 +539,7 @@
     <t>制冷启动温差</t>
   </si>
   <si>
-    <t>temperatureDifferenceDuringRefrigerationStartUp</t>
+    <t>refrigStartTDiff</t>
   </si>
   <si>
     <t>{"en":"Temperature difference during refrigeration start-up"}</t>
@@ -548,7 +548,7 @@
     <t>加热停止温差</t>
   </si>
   <si>
-    <t>heatingStopTemperatureDifference</t>
+    <t>heatStopTDiff</t>
   </si>
   <si>
     <t>{"en":"Heating stop temperature difference"}</t>
@@ -557,7 +557,7 @@
     <t>加热启动温差</t>
   </si>
   <si>
-    <t>heatingStartUpTemperatureDifference</t>
+    <t>heatStartTDiff</t>
   </si>
   <si>
     <t>{"en":"Heating start-up temperature difference"}</t>
@@ -566,7 +566,7 @@
     <t>水温控制选择</t>
   </si>
   <si>
-    <t>waterTemperatureControlSelection</t>
+    <t>waterTCtrlSel</t>
   </si>
   <si>
     <t>{"en":"Water temperature control selection"}</t>
@@ -575,7 +575,7 @@
     <t>补液泵强制补液</t>
   </si>
   <si>
-    <t>forcedFluidReplacementPump</t>
+    <t>forcedFluidReplPump</t>
   </si>
   <si>
     <t>{"en":"Forced fluid replacement pump"}</t>
@@ -588,7 +588,7 @@
     <t>RS485从站地址</t>
   </si>
   <si>
-    <t>rs485SlaveAddress</t>
+    <t>rs485SlaveAddr</t>
   </si>
   <si>
     <t>{"en":"RS485 slave address"}</t>
